--- a/artfynd/A 21862-2019 artfynd.xlsx
+++ b/artfynd/A 21862-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121984723</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>57769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21862-2019 artfynd.xlsx
+++ b/artfynd/A 21862-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121984723</v>
       </c>
       <c r="B2" t="n">
-        <v>57769</v>
+        <v>57773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21862-2019 artfynd.xlsx
+++ b/artfynd/A 21862-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121984723</v>
       </c>
       <c r="B2" t="n">
-        <v>57773</v>
+        <v>57777</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21862-2019 artfynd.xlsx
+++ b/artfynd/A 21862-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121984723</v>
       </c>
       <c r="B2" t="n">
-        <v>57777</v>
+        <v>57779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21862-2019 artfynd.xlsx
+++ b/artfynd/A 21862-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121984723</v>
       </c>
       <c r="B2" t="n">
-        <v>57779</v>
+        <v>57784</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
